--- a/StructureDefinition-lmdi-medication.xlsx
+++ b/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.4</t>
+    <t>1.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -1171,7 +1171,7 @@
     <t>Medication.form.coding</t>
   </si>
   <si>
-    <t>Kodet legemiddelform. Inntil videre begrenset til Legemiddelform (OID: 7448) og kodesetteksempel fra HL7 basert på SNOMED CT.</t>
+    <t>Kodet legemiddelform. Legemiddelform (OID: 7448) fra FEST og SNOMED CT er definert som slices. Andre kodesystemer er tillatt.</t>
   </si>
   <si>
     <t>Medication.form.coding.id</t>
@@ -11800,7 +11800,7 @@
         <v>77</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>190</v>

--- a/StructureDefinition-lmdi-medication.xlsx
+++ b/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.5</t>
+    <t>1.1.7</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-medication.xlsx
+++ b/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.7</t>
+    <t>1.1.8</t>
   </si>
   <si>
     <t>Name</t>
